--- a/EcomTest/target/classes/resources/testData.xlsx
+++ b/EcomTest/target/classes/resources/testData.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10855015\Desktop\E2ETest\E2ETestSuite\EcomTest\src\main\java\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D35243-6A04-4952-87ED-4D35F9DDCF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="70" windowWidth="13340" windowHeight="4300"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Categories" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="WebTestData" sheetId="2" r:id="rId2"/>
+    <sheet name="APITestData" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Categories</t>
   </si>
@@ -49,13 +55,55 @@
   </si>
   <si>
     <t>women</t>
+  </si>
+  <si>
+    <t>browser</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>Password@123</t>
+  </si>
+  <si>
+    <t>https://rahulshettyacademy.com/client/#/auth/login</t>
+  </si>
+  <si>
+    <t>yaser1@yaser.com</t>
+  </si>
+  <si>
+    <t>TestValue</t>
+  </si>
+  <si>
+    <t>LoginTest</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>baseURI</t>
+  </si>
+  <si>
+    <t>https://www.rahulshettyacademy.com/</t>
+  </si>
+  <si>
+    <t>loginTest</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,6 +116,13 @@
       <color rgb="FF000000"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -90,22 +145,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -143,7 +207,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -177,6 +241,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -211,9 +276,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -386,66 +452,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
     </row>
   </sheetData>
@@ -455,19 +521,102 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{CD5CB623-EF70-4A15-B4A1-68F4950F5CB8}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{FD6DE6EC-2A28-4FBA-AFAE-0055434A45A3}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{356BB3A7-935F-492C-80FD-84BE74300251}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>